--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/750000/Output_0_12.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/750000/Output_0_12.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>507843.8865985547</v>
+        <v>480499.7470222876</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>925658.2446351685</v>
+        <v>925399.3994514378</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18327269.62422524</v>
+        <v>18327015.9300607</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5571761.790766618</v>
+        <v>5571875.219309996</v>
       </c>
     </row>
     <row r="11">
@@ -700,22 +700,22 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>212.285385643442</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="W2" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X2" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y2" t="n">
-        <v>212.2728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C3" t="n">
-        <v>145.3912560091964</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>147.4450655646388</v>
+        <v>26.20075604774391</v>
       </c>
       <c r="E3" t="n">
         <v>157.6450804554009</v>
@@ -773,7 +773,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -825,13 +825,13 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>17.55829564281238</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>93.35918011667277</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -846,13 +846,13 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>44.30348359856715</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -883,31 +883,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F5" t="n">
-        <v>230.8476210749815</v>
+        <v>212.2853856434421</v>
       </c>
       <c r="G5" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -962,13 +962,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C6" t="n">
-        <v>145.3912560091964</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D6" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>157.6450804554009</v>
@@ -980,13 +980,13 @@
         <v>137.3435171632106</v>
       </c>
       <c r="H6" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1031,7 +1031,7 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>156.0287596262406</v>
       </c>
     </row>
     <row r="7">
@@ -1053,7 +1053,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>17.55829564281238</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1065,10 +1065,10 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>93.35918011667277</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1098,7 +1098,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1120,13 +1120,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -1138,13 +1138,13 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1165,13 +1165,13 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>71.01467844038818</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1186,10 +1186,10 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>212.2728</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1202,7 +1202,7 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>145.3912560091964</v>
+        <v>145.4467082856156</v>
       </c>
       <c r="D9" t="n">
         <v>147.4450655646388</v>
@@ -1299,13 +1299,13 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>17.55829564281241</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1320,13 +1320,13 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>44.30348359856712</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1363,22 +1363,22 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1.809496073036132</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1417,16 +1417,16 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>212.2728</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1439,7 +1439,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>114.2227459476827</v>
+        <v>75.98437144330408</v>
       </c>
       <c r="D12" t="n">
         <v>147.4450655646388</v>
@@ -1460,7 +1460,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1484,10 +1484,10 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -1496,7 +1496,7 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -1563,7 +1563,7 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R13" t="n">
-        <v>44.30348359856712</v>
+        <v>44.30348359856715</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1594,10 +1594,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>212.2853856434421</v>
       </c>
       <c r="C14" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X14" t="n">
-        <v>212.2728</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y14" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="15">
@@ -1679,13 +1679,13 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F15" t="n">
-        <v>123.5448804713173</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G15" t="n">
         <v>137.3435171632106</v>
@@ -1694,7 +1694,7 @@
         <v>112.2354442364965</v>
       </c>
       <c r="I15" t="n">
-        <v>89.39663285141508</v>
+        <v>63.16017003319293</v>
       </c>
       <c r="J15" t="n">
         <v>0.7465913262578567</v>
@@ -1721,13 +1721,13 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>171.6831711038378</v>
       </c>
       <c r="T15" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -1770,7 +1770,7 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1794,13 +1794,13 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>44.30348359856715</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1843,16 +1843,16 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>23.7861416288039</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1879,19 +1879,19 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S17" t="n">
-        <v>209.0200695862453</v>
+        <v>70.34400780127524</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
@@ -1910,31 +1910,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F18" t="n">
-        <v>123.5448804713173</v>
+        <v>19.15541836171557</v>
       </c>
       <c r="G18" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1964,7 +1964,7 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T18" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -2040,13 +2040,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -2080,10 +2080,10 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -2113,25 +2113,25 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>202.2946864288972</v>
       </c>
       <c r="T20" t="n">
-        <v>212.2728</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2150,25 +2150,25 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>73.86212647435181</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2198,25 +2198,25 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>83.03189205754168</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y21" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2292,7 +2292,7 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
@@ -2305,22 +2305,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>212.2728</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2362,13 +2362,13 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>202.2946864288972</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2384,19 +2384,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C24" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>137.3435171632106</v>
@@ -2405,10 +2405,10 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>53.17436456111953</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2432,13 +2432,13 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>171.6831711038378</v>
       </c>
       <c r="T24" t="n">
-        <v>50.66548574320777</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2453,7 +2453,7 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="25">
@@ -2554,19 +2554,19 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>230.8476210749815</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -2587,22 +2587,22 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>102.3382270926889</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -2630,7 +2630,7 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -2645,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -2669,28 +2669,28 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V27" t="n">
-        <v>199.6388549139498</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>3.833957768458675</v>
       </c>
       <c r="X27" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2745,10 +2745,10 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>47.02492433367365</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2763,7 +2763,7 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>8.75920136422792e-11</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -2827,28 +2827,28 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>80.33470701582003</v>
       </c>
       <c r="T29" t="n">
-        <v>212.272800000065</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U29" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2858,16 +2858,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>41.95719884904037</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -2876,13 +2876,13 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>50.0165318697929</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -2912,22 +2912,22 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y30" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2943,10 +2943,10 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -3022,16 +3022,16 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F32" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -3073,19 +3073,19 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>212.285385643442</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X32" t="n">
-        <v>212.2728</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -3098,28 +3098,28 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>63.50968227731285</v>
       </c>
       <c r="I33" t="n">
         <v>89.39663285141508</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -3155,16 +3155,16 @@
         <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>26.88730251793573</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -3237,10 +3237,10 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="X34" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
         <v>0</v>
@@ -3259,19 +3259,19 @@
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -3301,22 +3301,22 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>6.505388228106311e-11</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V35" t="n">
-        <v>212.2728</v>
+        <v>80.33470701582003</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X35" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
         <v>172.7084989883157</v>
@@ -3341,7 +3341,7 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>157.5478344350873</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -3350,13 +3350,13 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>8.051864102726135</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -3389,7 +3389,7 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V36" t="n">
         <v>232.8005871494253</v>
@@ -3453,13 +3453,13 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>44.30348359856712</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
         <v>0</v>
@@ -3490,13 +3490,13 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -3535,7 +3535,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -3547,19 +3547,19 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X38" t="n">
-        <v>202.2821007854552</v>
+        <v>212.2853856434421</v>
       </c>
       <c r="Y38" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -3578,19 +3578,19 @@
         <v>147.4450655646388</v>
       </c>
       <c r="E39" t="n">
-        <v>62.7829277908552</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>137.3435171632106</v>
       </c>
       <c r="H39" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3632,13 +3632,13 @@
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>241</v>
+        <v>239.083988567788</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="40">
@@ -3702,7 +3702,7 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -3711,7 +3711,7 @@
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
@@ -3727,16 +3727,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C41" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>190.3328114308427</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -3745,13 +3745,13 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -3772,7 +3772,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -3784,13 +3784,13 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>212.285385643442</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
@@ -3806,16 +3806,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D42" t="n">
         <v>147.4450655646388</v>
       </c>
       <c r="E42" t="n">
-        <v>62.0363364645973</v>
+        <v>53.24673895424847</v>
       </c>
       <c r="F42" t="n">
         <v>145.0692123933839</v>
@@ -3827,7 +3827,7 @@
         <v>112.2354442364965</v>
       </c>
       <c r="I42" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0.7465913262578567</v>
@@ -3869,7 +3869,7 @@
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -3948,7 +3948,7 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
         <v>0</v>
@@ -3967,25 +3967,25 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>212.285385643442</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F44" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4009,19 +4009,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>41.69029206467248</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -4046,28 +4046,28 @@
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D45" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>151.4329693160124</v>
+        <v>150.9993436125</v>
       </c>
       <c r="F45" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -4097,7 +4097,7 @@
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
@@ -4106,13 +4106,13 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="46">
@@ -4179,19 +4179,19 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="V46" t="n">
-        <v>0</v>
-      </c>
-      <c r="W46" t="n">
-        <v>0</v>
-      </c>
-      <c r="X46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4289,76 +4289,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K2" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L2" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M2" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N2" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O2" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P2" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q2" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R2" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S2" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T2" t="n">
-        <v>964</v>
+        <v>749.627473042513</v>
       </c>
       <c r="U2" t="n">
-        <v>964</v>
+        <v>749.627473042513</v>
       </c>
       <c r="V2" t="n">
-        <v>720.5656565656566</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="W2" t="n">
-        <v>477.1313131313132</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="X2" t="n">
-        <v>233.6969696969697</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="3">
@@ -4368,76 +4368,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>964</v>
+        <v>694.6722890434539</v>
       </c>
       <c r="C3" t="n">
-        <v>817.1401454452562</v>
+        <v>694.6722890434539</v>
       </c>
       <c r="D3" t="n">
-        <v>668.2057357840049</v>
+        <v>668.2068788942177</v>
       </c>
       <c r="E3" t="n">
-        <v>508.9682807785495</v>
+        <v>508.9694238887622</v>
       </c>
       <c r="F3" t="n">
-        <v>362.4337228054344</v>
+        <v>362.4348659156472</v>
       </c>
       <c r="G3" t="n">
-        <v>223.7028973880499</v>
+        <v>223.7040404982626</v>
       </c>
       <c r="H3" t="n">
-        <v>110.3337617956292</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I3" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J3" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K3" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L3" t="n">
-        <v>178.8354414866706</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M3" t="n">
-        <v>417.4254414866706</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N3" t="n">
-        <v>656.0154414866706</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="O3" t="n">
-        <v>894.6054414866707</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P3" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q3" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R3" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S3" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="T3" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="U3" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="V3" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="W3" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="X3" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="Y3" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
     </row>
     <row r="4">
@@ -4447,76 +4447,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C4" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D4" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E4" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F4" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G4" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H4" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I4" t="n">
-        <v>136.0766383258138</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J4" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K4" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L4" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M4" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N4" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P4" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="Q4" t="n">
-        <v>153.8122904902707</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="R4" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="S4" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T4" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U4" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V4" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W4" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X4" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y4" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="5">
@@ -4526,76 +4526,76 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>964</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="C5" t="n">
-        <v>964</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="D5" t="n">
-        <v>964</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="E5" t="n">
-        <v>964</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="F5" t="n">
-        <v>730.820584772746</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G5" t="n">
-        <v>487.3862413384025</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H5" t="n">
-        <v>243.9518979040591</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I5" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J5" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K5" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L5" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M5" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N5" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O5" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P5" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q5" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R5" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S5" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T5" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U5" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V5" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W5" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X5" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y5" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="6">
@@ -4605,76 +4605,76 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>964</v>
+        <v>638.2370107872948</v>
       </c>
       <c r="C6" t="n">
-        <v>817.1401454452562</v>
+        <v>463.7839815061678</v>
       </c>
       <c r="D6" t="n">
-        <v>668.2057357840049</v>
+        <v>463.7839815061678</v>
       </c>
       <c r="E6" t="n">
-        <v>508.9682807785495</v>
+        <v>304.5465265007123</v>
       </c>
       <c r="F6" t="n">
-        <v>362.4337228054344</v>
+        <v>158.0119685275972</v>
       </c>
       <c r="G6" t="n">
-        <v>223.7028973880499</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H6" t="n">
-        <v>110.3337617956292</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I6" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J6" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K6" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L6" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="M6" t="n">
-        <v>234.7819638733197</v>
+        <v>257.8852890990952</v>
       </c>
       <c r="N6" t="n">
-        <v>473.3719638733197</v>
+        <v>496.4894350879777</v>
       </c>
       <c r="O6" t="n">
-        <v>711.9619638733197</v>
+        <v>735.0935810768601</v>
       </c>
       <c r="P6" t="n">
-        <v>894.6054414866707</v>
+        <v>917.7370586902109</v>
       </c>
       <c r="Q6" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R6" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S6" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T6" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U6" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V6" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W6" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X6" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y6" t="n">
-        <v>964</v>
+        <v>806.4523478073629</v>
       </c>
     </row>
     <row r="7">
@@ -4684,76 +4684,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C7" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D7" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E7" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F7" t="n">
-        <v>136.0766383258138</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G7" t="n">
-        <v>136.0766383258138</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H7" t="n">
-        <v>136.0766383258138</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I7" t="n">
-        <v>136.0766383258138</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J7" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K7" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L7" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M7" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N7" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U7" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V7" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W7" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X7" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y7" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="8">
@@ -4763,76 +4763,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>262.7143434343434</v>
+        <v>730.8505943024719</v>
       </c>
       <c r="C8" t="n">
-        <v>19.28</v>
+        <v>730.8505943024719</v>
       </c>
       <c r="D8" t="n">
-        <v>19.28</v>
+        <v>487.4018176583718</v>
       </c>
       <c r="E8" t="n">
-        <v>19.28</v>
+        <v>487.4018176583718</v>
       </c>
       <c r="F8" t="n">
-        <v>19.28</v>
+        <v>487.4018176583718</v>
       </c>
       <c r="G8" t="n">
-        <v>19.28</v>
+        <v>487.4018176583718</v>
       </c>
       <c r="H8" t="n">
-        <v>19.28</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="I8" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J8" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K8" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L8" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M8" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N8" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O8" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P8" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q8" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R8" t="n">
-        <v>964</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="S8" t="n">
-        <v>964</v>
+        <v>730.8505943024719</v>
       </c>
       <c r="T8" t="n">
-        <v>964</v>
+        <v>730.8505943024719</v>
       </c>
       <c r="U8" t="n">
-        <v>964</v>
+        <v>730.8505943024719</v>
       </c>
       <c r="V8" t="n">
-        <v>964</v>
+        <v>730.8505943024719</v>
       </c>
       <c r="W8" t="n">
-        <v>964</v>
+        <v>730.8505943024719</v>
       </c>
       <c r="X8" t="n">
-        <v>749.5830303030303</v>
+        <v>730.8505943024719</v>
       </c>
       <c r="Y8" t="n">
-        <v>506.1486868686869</v>
+        <v>730.8505943024719</v>
       </c>
     </row>
     <row r="9">
@@ -4842,76 +4842,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C9" t="n">
-        <v>817.1401454452562</v>
+        <v>817.1412885554689</v>
       </c>
       <c r="D9" t="n">
-        <v>668.2057357840049</v>
+        <v>668.2068788942177</v>
       </c>
       <c r="E9" t="n">
-        <v>508.9682807785495</v>
+        <v>508.9694238887622</v>
       </c>
       <c r="F9" t="n">
-        <v>362.4337228054344</v>
+        <v>362.4348659156472</v>
       </c>
       <c r="G9" t="n">
-        <v>223.7028973880499</v>
+        <v>223.7040404982626</v>
       </c>
       <c r="H9" t="n">
-        <v>110.3337617956292</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I9" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J9" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K9" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L9" t="n">
-        <v>374.6006659261865</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M9" t="n">
-        <v>417.4254414866706</v>
+        <v>487.8483949674443</v>
       </c>
       <c r="N9" t="n">
-        <v>656.0154414866706</v>
+        <v>725.4530095217538</v>
       </c>
       <c r="O9" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P9" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q9" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R9" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S9" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T9" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U9" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V9" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W9" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X9" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y9" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="10">
@@ -4921,76 +4921,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C10" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D10" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E10" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="F10" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="G10" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="H10" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="I10" t="n">
-        <v>19.28</v>
+        <v>136.0777814360265</v>
       </c>
       <c r="J10" t="n">
-        <v>19.28</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="K10" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L10" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M10" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N10" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P10" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q10" t="n">
-        <v>64.03099353390618</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R10" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S10" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T10" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U10" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V10" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W10" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X10" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y10" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="11">
@@ -5000,76 +5000,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C11" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="D11" t="n">
-        <v>19.28</v>
+        <v>962.2293816994886</v>
       </c>
       <c r="E11" t="n">
-        <v>19.28</v>
+        <v>718.7806050553886</v>
       </c>
       <c r="F11" t="n">
-        <v>19.28</v>
+        <v>475.3318284112885</v>
       </c>
       <c r="G11" t="n">
-        <v>19.28</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="H11" t="n">
-        <v>19.28</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="I11" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J11" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K11" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L11" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M11" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N11" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O11" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P11" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q11" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R11" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S11" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T11" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U11" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V11" t="n">
-        <v>749.5830303030303</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W11" t="n">
-        <v>506.1486868686869</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X11" t="n">
-        <v>262.7143434343434</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y11" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="12">
@@ -5079,76 +5079,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>728.8478917682573</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="C12" t="n">
-        <v>613.471380709992</v>
+        <v>612.718391167419</v>
       </c>
       <c r="D12" t="n">
-        <v>464.5369710487408</v>
+        <v>463.7839815061678</v>
       </c>
       <c r="E12" t="n">
-        <v>305.2995160432853</v>
+        <v>304.5465265007123</v>
       </c>
       <c r="F12" t="n">
-        <v>158.7649580701702</v>
+        <v>158.0119685275972</v>
       </c>
       <c r="G12" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H12" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I12" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J12" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K12" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L12" t="n">
-        <v>19.28</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M12" t="n">
-        <v>234.7819638733197</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="N12" t="n">
-        <v>473.3719638733197</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="O12" t="n">
-        <v>711.9619638733197</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P12" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q12" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R12" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S12" t="n">
-        <v>964</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="T12" t="n">
-        <v>964</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="U12" t="n">
-        <v>964</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="V12" t="n">
-        <v>728.8478917682573</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="W12" t="n">
-        <v>728.8478917682573</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="X12" t="n">
-        <v>728.8478917682573</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="Y12" t="n">
-        <v>728.8478917682573</v>
+        <v>689.4702815141908</v>
       </c>
     </row>
     <row r="13">
@@ -5158,76 +5158,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L13" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M13" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N13" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O13" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P13" t="n">
-        <v>151.0633604548096</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="Q13" t="n">
-        <v>64.03099353390618</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="R13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="S13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="14">
@@ -5237,76 +5237,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>506.1486868686869</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C14" t="n">
-        <v>262.7143434343434</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D14" t="n">
-        <v>262.7143434343434</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E14" t="n">
-        <v>262.7143434343434</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F14" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G14" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H14" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I14" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J14" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K14" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L14" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M14" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N14" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O14" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P14" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q14" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R14" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S14" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T14" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U14" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V14" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W14" t="n">
-        <v>964</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="X14" t="n">
-        <v>749.5830303030303</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="Y14" t="n">
-        <v>506.1486868686869</v>
+        <v>233.7108255783361</v>
       </c>
     </row>
     <row r="15">
@@ -5316,76 +5316,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>487.2265313623206</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="C15" t="n">
-        <v>487.2265313623206</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="D15" t="n">
-        <v>487.2265313623206</v>
+        <v>641.7054013000538</v>
       </c>
       <c r="E15" t="n">
-        <v>487.2265313623206</v>
+        <v>482.4679462945983</v>
       </c>
       <c r="F15" t="n">
-        <v>362.4337228054344</v>
+        <v>335.9333883214833</v>
       </c>
       <c r="G15" t="n">
-        <v>223.7028973880499</v>
+        <v>197.2025629040988</v>
       </c>
       <c r="H15" t="n">
-        <v>110.3337617956292</v>
+        <v>83.83342731167816</v>
       </c>
       <c r="I15" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J15" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K15" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L15" t="n">
-        <v>374.6006659261865</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M15" t="n">
-        <v>374.6006659261865</v>
+        <v>487.8483949674443</v>
       </c>
       <c r="N15" t="n">
-        <v>542.7665223866492</v>
+        <v>487.8483949674443</v>
       </c>
       <c r="O15" t="n">
-        <v>781.3565223866492</v>
+        <v>726.4525409563269</v>
       </c>
       <c r="P15" t="n">
-        <v>964</v>
+        <v>909.0960185696777</v>
       </c>
       <c r="Q15" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R15" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S15" t="n">
-        <v>689.4131260035546</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="T15" t="n">
-        <v>487.2265313623206</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="U15" t="n">
-        <v>487.2265313623206</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="V15" t="n">
-        <v>487.2265313623206</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="W15" t="n">
-        <v>487.2265313623206</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="X15" t="n">
-        <v>487.2265313623206</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="Y15" t="n">
-        <v>487.2265313623206</v>
+        <v>790.6398109613051</v>
       </c>
     </row>
     <row r="16">
@@ -5395,76 +5395,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H16" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I16" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J16" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K16" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L16" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M16" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N16" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P16" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="Q16" t="n">
-        <v>153.8122904902707</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="R16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="S16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="17">
@@ -5474,76 +5474,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>742.7770012113231</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C17" t="n">
-        <v>742.7770012113231</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D17" t="n">
-        <v>742.7770012113231</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E17" t="n">
-        <v>742.7770012113231</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F17" t="n">
-        <v>718.7505955256626</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G17" t="n">
-        <v>475.3162520913191</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H17" t="n">
-        <v>231.8819086569757</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I17" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J17" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K17" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L17" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M17" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N17" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O17" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P17" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q17" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R17" t="n">
-        <v>953.9083846317729</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="S17" t="n">
-        <v>742.7770012113231</v>
+        <v>731.528039392485</v>
       </c>
       <c r="T17" t="n">
-        <v>742.7770012113231</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="U17" t="n">
-        <v>742.7770012113231</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="V17" t="n">
-        <v>742.7770012113231</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W17" t="n">
-        <v>742.7770012113231</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X17" t="n">
-        <v>742.7770012113231</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y17" t="n">
-        <v>742.7770012113231</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="18">
@@ -5553,76 +5553,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>487.2265313623206</v>
+        <v>521.2549444941228</v>
       </c>
       <c r="C18" t="n">
-        <v>487.2265313623206</v>
+        <v>346.8019152129958</v>
       </c>
       <c r="D18" t="n">
-        <v>487.2265313623206</v>
+        <v>197.8675055517446</v>
       </c>
       <c r="E18" t="n">
-        <v>487.2265313623206</v>
+        <v>38.63005054628906</v>
       </c>
       <c r="F18" t="n">
-        <v>362.4337228054344</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G18" t="n">
-        <v>223.7028973880499</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H18" t="n">
-        <v>110.3337617956292</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I18" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J18" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K18" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L18" t="n">
-        <v>249.2431058683491</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="M18" t="n">
-        <v>304.1765223866491</v>
+        <v>234.810827406191</v>
       </c>
       <c r="N18" t="n">
-        <v>542.7665223866492</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O18" t="n">
-        <v>781.3565223866492</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P18" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q18" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R18" t="n">
-        <v>862.8304705528857</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S18" t="n">
-        <v>689.4131260035546</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="T18" t="n">
-        <v>487.2265313623206</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="U18" t="n">
-        <v>487.2265313623206</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="V18" t="n">
-        <v>487.2265313623206</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="W18" t="n">
-        <v>487.2265313623206</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="X18" t="n">
-        <v>487.2265313623206</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="Y18" t="n">
-        <v>487.2265313623206</v>
+        <v>689.4702815141908</v>
       </c>
     </row>
     <row r="19">
@@ -5632,76 +5632,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L19" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M19" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N19" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S19" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T19" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="20">
@@ -5711,76 +5711,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>19.28</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="C20" t="n">
-        <v>19.28</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="D20" t="n">
-        <v>19.28</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="E20" t="n">
-        <v>19.28</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="F20" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="G20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K20" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L20" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M20" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N20" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O20" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q20" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R20" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S20" t="n">
-        <v>964</v>
+        <v>749.627473042513</v>
       </c>
       <c r="T20" t="n">
-        <v>749.5830303030303</v>
+        <v>749.627473042513</v>
       </c>
       <c r="U20" t="n">
-        <v>506.1486868686869</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="V20" t="n">
-        <v>262.7143434343434</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="W20" t="n">
-        <v>19.28</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="X20" t="n">
-        <v>19.28</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="Y20" t="n">
-        <v>19.28</v>
+        <v>506.1786963984129</v>
       </c>
     </row>
     <row r="21">
@@ -5790,76 +5790,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>582.822356685715</v>
+        <v>193.7341723913397</v>
       </c>
       <c r="C21" t="n">
-        <v>582.822356685715</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D21" t="n">
-        <v>582.822356685715</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E21" t="n">
-        <v>508.2141481257637</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F21" t="n">
-        <v>361.6795901526487</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G21" t="n">
-        <v>222.9487647352642</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H21" t="n">
-        <v>109.5796291428435</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K21" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L21" t="n">
-        <v>249.2431058683491</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M21" t="n">
-        <v>487.8331058683492</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N21" t="n">
-        <v>726.4231058683491</v>
+        <v>851.8101010141643</v>
       </c>
       <c r="O21" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P21" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S21" t="n">
-        <v>790.5826554506689</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T21" t="n">
-        <v>790.5826554506689</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U21" t="n">
-        <v>790.5826554506689</v>
+        <v>880.1865574727153</v>
       </c>
       <c r="V21" t="n">
-        <v>790.5826554506689</v>
+        <v>645.0344492409727</v>
       </c>
       <c r="W21" t="n">
-        <v>790.5826554506689</v>
+        <v>401.5856725968725</v>
       </c>
       <c r="X21" t="n">
-        <v>790.5826554506689</v>
+        <v>193.7341723913397</v>
       </c>
       <c r="Y21" t="n">
-        <v>582.822356685715</v>
+        <v>193.7341723913397</v>
       </c>
     </row>
     <row r="22">
@@ -5869,76 +5869,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L22" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M22" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N22" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S22" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T22" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U22" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V22" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W22" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="23">
@@ -5948,76 +5948,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>720.5656565656566</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="C23" t="n">
-        <v>477.1313131313132</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="D23" t="n">
-        <v>262.7143434343434</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="E23" t="n">
-        <v>262.7143434343434</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F23" t="n">
-        <v>262.7143434343434</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K23" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L23" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M23" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N23" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O23" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q23" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R23" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S23" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="T23" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="U23" t="n">
-        <v>964</v>
+        <v>710.516763498309</v>
       </c>
       <c r="V23" t="n">
-        <v>964</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="W23" t="n">
-        <v>964</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="X23" t="n">
-        <v>964</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="Y23" t="n">
-        <v>964</v>
+        <v>262.7299197543128</v>
       </c>
     </row>
     <row r="24">
@@ -6027,76 +6027,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>638.2358676770821</v>
+        <v>212.4775805350491</v>
       </c>
       <c r="C24" t="n">
-        <v>463.782838395955</v>
+        <v>212.4775805350491</v>
       </c>
       <c r="D24" t="n">
-        <v>463.782838395955</v>
+        <v>212.4775805350491</v>
       </c>
       <c r="E24" t="n">
-        <v>304.5453833904995</v>
+        <v>212.4775805350491</v>
       </c>
       <c r="F24" t="n">
-        <v>158.0108254173845</v>
+        <v>212.4775805350491</v>
       </c>
       <c r="G24" t="n">
-        <v>19.28</v>
+        <v>73.74675511766463</v>
       </c>
       <c r="H24" t="n">
-        <v>19.28</v>
+        <v>73.74675511766463</v>
       </c>
       <c r="I24" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L24" t="n">
-        <v>19.28</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M24" t="n">
-        <v>234.7819638733197</v>
+        <v>487.8483949674443</v>
       </c>
       <c r="N24" t="n">
-        <v>473.3719638733197</v>
+        <v>726.4525409563269</v>
       </c>
       <c r="O24" t="n">
-        <v>711.9619638733197</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P24" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R24" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S24" t="n">
-        <v>689.4131260035546</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="T24" t="n">
-        <v>638.2358676770821</v>
+        <v>588.4532163200711</v>
       </c>
       <c r="U24" t="n">
-        <v>638.2358676770821</v>
+        <v>588.4532163200711</v>
       </c>
       <c r="V24" t="n">
-        <v>638.2358676770821</v>
+        <v>588.4532163200711</v>
       </c>
       <c r="W24" t="n">
-        <v>638.2358676770821</v>
+        <v>588.4532163200711</v>
       </c>
       <c r="X24" t="n">
-        <v>638.2358676770821</v>
+        <v>588.4532163200711</v>
       </c>
       <c r="Y24" t="n">
-        <v>638.2358676770821</v>
+        <v>380.6929175551172</v>
       </c>
     </row>
     <row r="25">
@@ -6106,76 +6106,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L25" t="n">
-        <v>856.7818345174422</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M25" t="n">
-        <v>895.9698727096644</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N25" t="n">
-        <v>939.6607233651007</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="26">
@@ -6185,76 +6185,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C26" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D26" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E26" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F26" t="n">
-        <v>730.820584772746</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G26" t="n">
-        <v>487.3862413384025</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H26" t="n">
-        <v>243.9518979040591</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I26" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K26" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L26" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M26" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N26" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O26" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q26" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R26" t="n">
-        <v>964</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="S26" t="n">
-        <v>964</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="T26" t="n">
-        <v>964</v>
+        <v>366.1018663125844</v>
       </c>
       <c r="U26" t="n">
-        <v>964</v>
+        <v>122.6530896684844</v>
       </c>
       <c r="V26" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W26" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X26" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y26" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="27">
@@ -6264,76 +6264,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>178.5174550054555</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="C27" t="n">
-        <v>178.5174550054555</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="D27" t="n">
-        <v>178.5174550054555</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="E27" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="F27" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="G27" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H27" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I27" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K27" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L27" t="n">
-        <v>249.2431058683491</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M27" t="n">
-        <v>487.8331058683492</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="N27" t="n">
-        <v>487.8331058683492</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O27" t="n">
-        <v>711.9619638733197</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P27" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R27" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S27" t="n">
-        <v>964</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="T27" t="n">
-        <v>964</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="U27" t="n">
-        <v>964</v>
+        <v>259.0600686093459</v>
       </c>
       <c r="V27" t="n">
-        <v>762.3445909960103</v>
+        <v>23.90796037760316</v>
       </c>
       <c r="W27" t="n">
-        <v>762.3445909960103</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="X27" t="n">
-        <v>554.4930907904775</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="Y27" t="n">
-        <v>346.7327920255235</v>
+        <v>20.03527576299844</v>
       </c>
     </row>
     <row r="28">
@@ -6343,76 +6343,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L28" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M28" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N28" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q28" t="n">
-        <v>153.8122904902707</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="R28" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="S28" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T28" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U28" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V28" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="29">
@@ -6422,76 +6422,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J29" t="n">
-        <v>19.27999999991152</v>
+        <v>19.28114311021275</v>
       </c>
       <c r="K29" t="n">
-        <v>122.2950059108339</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L29" t="n">
-        <v>302.3708574954925</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M29" t="n">
-        <v>519.3464847583966</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N29" t="n">
-        <v>725.201006965636</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O29" t="n">
-        <v>874.3959571082841</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P29" t="n">
-        <v>964.0000000000657</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q29" t="n">
-        <v>964.0000000000657</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R29" t="n">
-        <v>964.0000000000657</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="S29" t="n">
-        <v>964.0000000000657</v>
+        <v>731.528039392485</v>
       </c>
       <c r="T29" t="n">
-        <v>749.5830303030303</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="U29" t="n">
-        <v>506.1486868686869</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="V29" t="n">
-        <v>506.1486868686869</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W29" t="n">
-        <v>506.1486868686869</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X29" t="n">
-        <v>262.7143434343434</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="30">
@@ -6501,76 +6501,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>69.80174936342718</v>
+        <v>385.8037236438013</v>
       </c>
       <c r="C30" t="n">
-        <v>69.80174936342718</v>
+        <v>211.3506943626743</v>
       </c>
       <c r="D30" t="n">
-        <v>69.80174936342718</v>
+        <v>62.41628470142305</v>
       </c>
       <c r="E30" t="n">
-        <v>69.80174936342718</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="F30" t="n">
-        <v>69.80174936342718</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="G30" t="n">
-        <v>69.80174936342718</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H30" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I30" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L30" t="n">
-        <v>249.2431058683491</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M30" t="n">
-        <v>417.4254414866706</v>
+        <v>487.8483949674443</v>
       </c>
       <c r="N30" t="n">
-        <v>656.0154414866706</v>
+        <v>726.4525409563269</v>
       </c>
       <c r="O30" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P30" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T30" t="n">
-        <v>964</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="U30" t="n">
-        <v>964</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="V30" t="n">
-        <v>728.8478917682573</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="W30" t="n">
-        <v>485.4135483339139</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="X30" t="n">
-        <v>277.5620481283811</v>
+        <v>554.0190606638694</v>
       </c>
       <c r="Y30" t="n">
-        <v>69.80174936342718</v>
+        <v>554.0190606638694</v>
       </c>
     </row>
     <row r="31">
@@ -6580,76 +6580,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C31" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="D31" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="E31" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="F31" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="G31" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="H31" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="I31" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="J31" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="K31" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="L31" t="n">
-        <v>46.59412500771298</v>
+        <v>856.8389900280785</v>
       </c>
       <c r="M31" t="n">
-        <v>85.78216319993516</v>
+        <v>896.0270282203006</v>
       </c>
       <c r="N31" t="n">
-        <v>129.4730138553714</v>
+        <v>939.7178788757369</v>
       </c>
       <c r="O31" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P31" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q31" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R31" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S31" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T31" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U31" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V31" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W31" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X31" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y31" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="32">
@@ -6659,76 +6659,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>506.1486868686869</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="C32" t="n">
-        <v>506.1486868686869</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="D32" t="n">
-        <v>506.1486868686869</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="E32" t="n">
-        <v>506.1486868686869</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F32" t="n">
-        <v>262.7143434343434</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G32" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H32" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I32" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J32" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K32" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L32" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M32" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N32" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O32" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P32" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q32" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R32" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S32" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T32" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U32" t="n">
-        <v>964</v>
+        <v>749.627473042513</v>
       </c>
       <c r="V32" t="n">
-        <v>964</v>
+        <v>749.627473042513</v>
       </c>
       <c r="W32" t="n">
-        <v>964</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="X32" t="n">
-        <v>749.5830303030303</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="Y32" t="n">
-        <v>506.1486868686869</v>
+        <v>506.1786963984129</v>
       </c>
     </row>
     <row r="33">
@@ -6738,76 +6738,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>109.5796291428435</v>
+        <v>795.8418184905681</v>
       </c>
       <c r="C33" t="n">
-        <v>109.5796291428435</v>
+        <v>621.3887892094411</v>
       </c>
       <c r="D33" t="n">
-        <v>109.5796291428435</v>
+        <v>472.4543795481899</v>
       </c>
       <c r="E33" t="n">
-        <v>109.5796291428435</v>
+        <v>313.2169245427344</v>
       </c>
       <c r="F33" t="n">
-        <v>109.5796291428435</v>
+        <v>313.2169245427344</v>
       </c>
       <c r="G33" t="n">
-        <v>109.5796291428435</v>
+        <v>174.4860991253499</v>
       </c>
       <c r="H33" t="n">
-        <v>109.5796291428435</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I33" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J33" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K33" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L33" t="n">
-        <v>19.28</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M33" t="n">
-        <v>257.87</v>
+        <v>486.8488635328713</v>
       </c>
       <c r="N33" t="n">
-        <v>473.3719638733197</v>
+        <v>725.4530095217538</v>
       </c>
       <c r="O33" t="n">
-        <v>711.9619638733197</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P33" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q33" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R33" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S33" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T33" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U33" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V33" t="n">
-        <v>936.8411085677417</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W33" t="n">
-        <v>693.4067651333983</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X33" t="n">
-        <v>485.5552649278655</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y33" t="n">
-        <v>277.7949661629116</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="34">
@@ -6817,76 +6817,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="C34" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="D34" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="E34" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="F34" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="G34" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="H34" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="I34" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="J34" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="K34" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="L34" t="n">
-        <v>856.7818345174422</v>
+        <v>856.8389900280785</v>
       </c>
       <c r="M34" t="n">
-        <v>895.9698727096644</v>
+        <v>896.0270282203006</v>
       </c>
       <c r="N34" t="n">
-        <v>939.6607233651007</v>
+        <v>939.7178788757369</v>
       </c>
       <c r="O34" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P34" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q34" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R34" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S34" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T34" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U34" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V34" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W34" t="n">
-        <v>964</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="X34" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="Y34" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
     </row>
     <row r="35">
@@ -6896,76 +6896,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>749.5830303030303</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C35" t="n">
-        <v>749.5830303030303</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D35" t="n">
-        <v>506.1486868686869</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E35" t="n">
-        <v>506.1486868686869</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F35" t="n">
-        <v>262.7143434343434</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G35" t="n">
-        <v>262.7143434343434</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H35" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I35" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J35" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K35" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L35" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M35" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N35" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O35" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P35" t="n">
-        <v>964.0000000000657</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q35" t="n">
-        <v>964.0000000000657</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R35" t="n">
-        <v>964</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="S35" t="n">
-        <v>964</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="T35" t="n">
-        <v>964</v>
+        <v>587.3248651012614</v>
       </c>
       <c r="U35" t="n">
-        <v>964</v>
+        <v>343.8760884571613</v>
       </c>
       <c r="V35" t="n">
-        <v>749.5830303030303</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="W35" t="n">
-        <v>749.5830303030303</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X35" t="n">
-        <v>749.5830303030303</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y35" t="n">
-        <v>749.5830303030303</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="36">
@@ -6975,76 +6975,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>352.8722559832354</v>
+        <v>292.9211302503287</v>
       </c>
       <c r="C36" t="n">
-        <v>178.4192267021084</v>
+        <v>118.4681009692017</v>
       </c>
       <c r="D36" t="n">
-        <v>178.4192267021084</v>
+        <v>118.4681009692017</v>
       </c>
       <c r="E36" t="n">
-        <v>19.28</v>
+        <v>118.4681009692017</v>
       </c>
       <c r="F36" t="n">
-        <v>19.28</v>
+        <v>118.4681009692017</v>
       </c>
       <c r="G36" t="n">
-        <v>19.28</v>
+        <v>118.4681009692017</v>
       </c>
       <c r="H36" t="n">
-        <v>19.28</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I36" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J36" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K36" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L36" t="n">
-        <v>374.6006659261865</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M36" t="n">
-        <v>473.3719638733197</v>
+        <v>486.8488635328713</v>
       </c>
       <c r="N36" t="n">
-        <v>473.3719638733197</v>
+        <v>725.4530095217538</v>
       </c>
       <c r="O36" t="n">
-        <v>711.9619638733197</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P36" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q36" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R36" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S36" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T36" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U36" t="n">
-        <v>964</v>
+        <v>735.8335372470253</v>
       </c>
       <c r="V36" t="n">
-        <v>728.8478917682573</v>
+        <v>500.6814290152826</v>
       </c>
       <c r="W36" t="n">
-        <v>728.8478917682573</v>
+        <v>500.6814290152826</v>
       </c>
       <c r="X36" t="n">
-        <v>728.8478917682573</v>
+        <v>500.6814290152826</v>
       </c>
       <c r="Y36" t="n">
-        <v>521.0875930033035</v>
+        <v>292.9211302503287</v>
       </c>
     </row>
     <row r="37">
@@ -7054,76 +7054,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L37" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M37" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N37" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O37" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P37" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q37" t="n">
-        <v>64.03099353390618</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R37" t="n">
-        <v>64.03099353390618</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="S37" t="n">
-        <v>64.03099353390618</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T37" t="n">
-        <v>64.03099353390618</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U37" t="n">
-        <v>64.03099353390618</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="38">
@@ -7133,76 +7133,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>262.7143434343434</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="C38" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="D38" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E38" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F38" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G38" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H38" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I38" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J38" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K38" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L38" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M38" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N38" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O38" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P38" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q38" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R38" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S38" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T38" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U38" t="n">
-        <v>953.9083846317729</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="V38" t="n">
-        <v>953.9083846317729</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="W38" t="n">
-        <v>953.9083846317729</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="X38" t="n">
-        <v>749.5830303030303</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="Y38" t="n">
-        <v>506.1486868686869</v>
+        <v>262.7299197543128</v>
       </c>
     </row>
     <row r="39">
@@ -7212,76 +7212,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>720.5656565656566</v>
+        <v>306.9463781888485</v>
       </c>
       <c r="C39" t="n">
-        <v>720.5656565656566</v>
+        <v>306.9463781888485</v>
       </c>
       <c r="D39" t="n">
-        <v>571.6312469044053</v>
+        <v>158.0119685275972</v>
       </c>
       <c r="E39" t="n">
-        <v>508.2141481257637</v>
+        <v>158.0119685275972</v>
       </c>
       <c r="F39" t="n">
-        <v>361.6795901526487</v>
+        <v>158.0119685275972</v>
       </c>
       <c r="G39" t="n">
-        <v>222.9487647352642</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H39" t="n">
-        <v>109.5796291428435</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I39" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J39" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K39" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L39" t="n">
-        <v>374.6006659261865</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M39" t="n">
-        <v>486.8199999999999</v>
+        <v>487.8483949674443</v>
       </c>
       <c r="N39" t="n">
-        <v>725.41</v>
+        <v>726.4525409563269</v>
       </c>
       <c r="O39" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="P39" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q39" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R39" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S39" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T39" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U39" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V39" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W39" t="n">
-        <v>720.5656565656566</v>
+        <v>722.5581771593352</v>
       </c>
       <c r="X39" t="n">
-        <v>720.5656565656566</v>
+        <v>514.7066769538023</v>
       </c>
       <c r="Y39" t="n">
-        <v>720.5656565656566</v>
+        <v>306.9463781888485</v>
       </c>
     </row>
     <row r="40">
@@ -7291,76 +7291,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="C40" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="D40" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="E40" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="F40" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="G40" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="H40" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="I40" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="J40" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="K40" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="L40" t="n">
-        <v>856.7818345174422</v>
+        <v>856.8389900280785</v>
       </c>
       <c r="M40" t="n">
-        <v>895.9698727096644</v>
+        <v>896.0270282203006</v>
       </c>
       <c r="N40" t="n">
-        <v>939.6607233651007</v>
+        <v>939.7178788757369</v>
       </c>
       <c r="O40" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P40" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q40" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R40" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S40" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T40" t="n">
-        <v>964</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="U40" t="n">
-        <v>964</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="V40" t="n">
-        <v>964</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="W40" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="X40" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="Y40" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
     </row>
     <row r="41">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>710.4740411974295</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="C41" t="n">
-        <v>467.0396977630861</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="D41" t="n">
-        <v>223.6053543287427</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="E41" t="n">
-        <v>31.34998924708335</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="F41" t="n">
-        <v>31.34998924708335</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="G41" t="n">
-        <v>31.34998924708335</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="H41" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I41" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J41" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K41" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L41" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M41" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N41" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O41" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P41" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q41" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R41" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S41" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T41" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U41" t="n">
-        <v>953.9083846317729</v>
+        <v>749.627473042513</v>
       </c>
       <c r="V41" t="n">
-        <v>953.9083846317729</v>
+        <v>749.627473042513</v>
       </c>
       <c r="W41" t="n">
-        <v>710.4740411974295</v>
+        <v>749.627473042513</v>
       </c>
       <c r="X41" t="n">
-        <v>710.4740411974295</v>
+        <v>749.627473042513</v>
       </c>
       <c r="Y41" t="n">
-        <v>710.4740411974295</v>
+        <v>749.627473042513</v>
       </c>
     </row>
     <row r="42">
@@ -7449,76 +7449,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>720.5656565656566</v>
+        <v>795.8418184905681</v>
       </c>
       <c r="C42" t="n">
-        <v>720.5656565656566</v>
+        <v>621.3887892094411</v>
       </c>
       <c r="D42" t="n">
-        <v>571.6312469044053</v>
+        <v>472.4543795481899</v>
       </c>
       <c r="E42" t="n">
-        <v>508.9682807785495</v>
+        <v>418.6697947459187</v>
       </c>
       <c r="F42" t="n">
-        <v>362.4337228054344</v>
+        <v>272.1352367728036</v>
       </c>
       <c r="G42" t="n">
-        <v>223.7028973880499</v>
+        <v>133.4044113554191</v>
       </c>
       <c r="H42" t="n">
-        <v>110.3337617956292</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I42" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J42" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K42" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L42" t="n">
-        <v>249.2431058683491</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="M42" t="n">
-        <v>487.8331058683492</v>
+        <v>257.8852890990952</v>
       </c>
       <c r="N42" t="n">
-        <v>726.4231058683491</v>
+        <v>496.4894350879777</v>
       </c>
       <c r="O42" t="n">
-        <v>781.3565223866492</v>
+        <v>735.0935810768601</v>
       </c>
       <c r="P42" t="n">
-        <v>964</v>
+        <v>917.7370586902109</v>
       </c>
       <c r="Q42" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R42" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S42" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T42" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U42" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V42" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W42" t="n">
-        <v>720.5656565656566</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X42" t="n">
-        <v>720.5656565656566</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y42" t="n">
-        <v>720.5656565656566</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="43">
@@ -7528,76 +7528,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L43" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M43" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N43" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O43" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P43" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q43" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R43" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="S43" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T43" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U43" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V43" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="44">
@@ -7607,76 +7607,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>475.3162520913191</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C44" t="n">
-        <v>475.3162520913191</v>
+        <v>749.627473042513</v>
       </c>
       <c r="D44" t="n">
-        <v>475.3162520913191</v>
+        <v>749.627473042513</v>
       </c>
       <c r="E44" t="n">
-        <v>475.3162520913191</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="F44" t="n">
-        <v>231.8819086569757</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="G44" t="n">
-        <v>231.8819086569757</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H44" t="n">
-        <v>231.8819086569757</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I44" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J44" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K44" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L44" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M44" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N44" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O44" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P44" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q44" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R44" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S44" t="n">
-        <v>742.7770012113231</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T44" t="n">
-        <v>517.427658217251</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U44" t="n">
-        <v>475.3162520913191</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V44" t="n">
-        <v>475.3162520913191</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W44" t="n">
-        <v>475.3162520913191</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X44" t="n">
-        <v>475.3162520913191</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y44" t="n">
-        <v>475.3162520913191</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="45">
@@ -7686,76 +7686,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>720.5656565656566</v>
+        <v>346.2587618989155</v>
       </c>
       <c r="C45" t="n">
-        <v>720.5656565656566</v>
+        <v>171.8057326177884</v>
       </c>
       <c r="D45" t="n">
-        <v>571.6312469044053</v>
+        <v>171.8057326177884</v>
       </c>
       <c r="E45" t="n">
-        <v>418.6686516357059</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F45" t="n">
-        <v>272.1340936625909</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G45" t="n">
-        <v>133.4032682452064</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H45" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I45" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J45" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K45" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L45" t="n">
-        <v>234.7819638733197</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M45" t="n">
-        <v>234.7819638733197</v>
+        <v>487.8483949674443</v>
       </c>
       <c r="N45" t="n">
-        <v>473.3719638733197</v>
+        <v>726.4525409563269</v>
       </c>
       <c r="O45" t="n">
-        <v>711.9619638733197</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P45" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q45" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R45" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S45" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T45" t="n">
-        <v>964</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="U45" t="n">
-        <v>964</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="V45" t="n">
-        <v>964</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="W45" t="n">
-        <v>720.5656565656566</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="X45" t="n">
-        <v>720.5656565656566</v>
+        <v>554.0190606638694</v>
       </c>
       <c r="Y45" t="n">
-        <v>720.5656565656566</v>
+        <v>346.2587618989155</v>
       </c>
     </row>
     <row r="46">
@@ -7765,76 +7765,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L46" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M46" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N46" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O46" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P46" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q46" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R46" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S46" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T46" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U46" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V46" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W46" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X46" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
   </sheetData>
@@ -7971,7 +7971,7 @@
         <v>437.3469244119842</v>
       </c>
       <c r="O2" t="n">
-        <v>380.7436030804994</v>
+        <v>380.8001812627454</v>
       </c>
       <c r="P2" t="n">
         <v>321.7987081714826</v>
@@ -8038,22 +8038,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K3" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L3" t="n">
-        <v>299.7214923926728</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M3" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N3" t="n">
-        <v>372.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O3" t="n">
-        <v>383.5962444444444</v>
+        <v>242.4075215744184</v>
       </c>
       <c r="P3" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q3" t="n">
         <v>210.0772877358491</v>
@@ -8205,7 +8205,7 @@
         <v>449.5135334928325</v>
       </c>
       <c r="N5" t="n">
-        <v>437.2903462297383</v>
+        <v>437.3469244119842</v>
       </c>
       <c r="O5" t="n">
         <v>380.8001812627454</v>
@@ -8275,25 +8275,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K6" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L6" t="n">
         <v>138.5543797798742</v>
       </c>
       <c r="M6" t="n">
-        <v>233.1889872709904</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N6" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O6" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P6" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q6" t="n">
-        <v>210.0772877358491</v>
+        <v>186.7697506723097</v>
       </c>
       <c r="R6" t="n">
         <v>45.52166981132082</v>
@@ -8433,7 +8433,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K8" t="n">
-        <v>324.1454125711647</v>
+        <v>324.1454125711648</v>
       </c>
       <c r="L8" t="n">
         <v>417.6612145504504</v>
@@ -8448,7 +8448,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P8" t="n">
-        <v>321.7421299892367</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q8" t="n">
         <v>212.3149906599047</v>
@@ -8512,25 +8512,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K9" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L9" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M9" t="n">
-        <v>185.3913829730123</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N9" t="n">
-        <v>372.3417120833333</v>
+        <v>371.3463732493024</v>
       </c>
       <c r="O9" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P9" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q9" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R9" t="n">
         <v>45.52166981132082</v>
@@ -8670,7 +8670,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K11" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L11" t="n">
         <v>417.6612145504504</v>
@@ -8749,25 +8749,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K12" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L12" t="n">
-        <v>138.5543797798742</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M12" t="n">
-        <v>359.81278530921</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N12" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O12" t="n">
-        <v>383.5962444444444</v>
+        <v>312.5030352242461</v>
       </c>
       <c r="P12" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q12" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R12" t="n">
         <v>45.52166981132082</v>
@@ -8913,7 +8913,7 @@
         <v>417.6612145504504</v>
       </c>
       <c r="M14" t="n">
-        <v>449.4569553105865</v>
+        <v>449.5135334928325</v>
       </c>
       <c r="N14" t="n">
         <v>437.3469244119842</v>
@@ -8986,25 +8986,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K15" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L15" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M15" t="n">
-        <v>142.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N15" t="n">
-        <v>301.2062135585481</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O15" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P15" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q15" t="n">
-        <v>139.9817740860215</v>
+        <v>195.4980740263837</v>
       </c>
       <c r="R15" t="n">
         <v>45.52166981132082</v>
@@ -9159,7 +9159,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P17" t="n">
-        <v>321.7421299892367</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q17" t="n">
         <v>212.3149906599047</v>
@@ -9226,22 +9226,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L18" t="n">
-        <v>370.8403453034592</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M18" t="n">
-        <v>197.6223334354527</v>
+        <v>359.8407857361378</v>
       </c>
       <c r="N18" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O18" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P18" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q18" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R18" t="n">
         <v>45.52166981132082</v>
@@ -9381,7 +9381,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K20" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L20" t="n">
         <v>417.6612145504504</v>
@@ -9460,25 +9460,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K21" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L21" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M21" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N21" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O21" t="n">
-        <v>312.4773915336581</v>
+        <v>255.9771075721939</v>
       </c>
       <c r="P21" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q21" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9618,7 +9618,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K23" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L23" t="n">
         <v>417.6612145504504</v>
@@ -9700,22 +9700,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L24" t="n">
-        <v>138.5543797798742</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M24" t="n">
-        <v>359.81278530921</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N24" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O24" t="n">
-        <v>383.5962444444444</v>
+        <v>198.1125443848066</v>
       </c>
       <c r="P24" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q24" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9855,7 +9855,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K26" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L26" t="n">
         <v>417.6612145504504</v>
@@ -9934,19 +9934,19 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K27" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L27" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M27" t="n">
-        <v>383.1340339220183</v>
+        <v>241.9453110519923</v>
       </c>
       <c r="N27" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O27" t="n">
-        <v>368.9890303080512</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P27" t="n">
         <v>318.4627686399372</v>
@@ -10107,7 +10107,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P29" t="n">
-        <v>321.7421299893924</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q29" t="n">
         <v>212.3149906599047</v>
@@ -10177,19 +10177,19 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M30" t="n">
-        <v>312.0151810112319</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N30" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O30" t="n">
-        <v>383.5962444444444</v>
+        <v>382.6009056104135</v>
       </c>
       <c r="P30" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q30" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10344,7 +10344,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P32" t="n">
-        <v>321.7421299892367</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q32" t="n">
         <v>212.3149906599047</v>
@@ -10411,22 +10411,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L33" t="n">
-        <v>138.5543797798742</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M33" t="n">
-        <v>383.1340339220183</v>
+        <v>382.1386950879875</v>
       </c>
       <c r="N33" t="n">
-        <v>349.020463470525</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O33" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P33" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q33" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10581,7 +10581,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P35" t="n">
-        <v>321.7421299893031</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q35" t="n">
         <v>212.3149906599047</v>
@@ -10645,25 +10645,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K36" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L36" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M36" t="n">
-        <v>241.9030217474054</v>
+        <v>382.1386950879875</v>
       </c>
       <c r="N36" t="n">
-        <v>131.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O36" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P36" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q36" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R36" t="n">
         <v>45.52166981132082</v>
@@ -10803,7 +10803,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K38" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711648</v>
       </c>
       <c r="L38" t="n">
         <v>417.6612145504504</v>
@@ -10882,25 +10882,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K39" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L39" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M39" t="n">
-        <v>255.4868966228399</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N39" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O39" t="n">
-        <v>383.5962444444444</v>
+        <v>312.5053919605859</v>
       </c>
       <c r="P39" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q39" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R39" t="n">
         <v>45.52166981132082</v>
@@ -11040,7 +11040,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K41" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L41" t="n">
         <v>417.6612145504504</v>
@@ -11122,22 +11122,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L42" t="n">
-        <v>370.8403453034592</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M42" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N42" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O42" t="n">
-        <v>198.0845439578789</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P42" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q42" t="n">
-        <v>139.9817740860215</v>
+        <v>186.7697506723097</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -11280,7 +11280,7 @@
         <v>324.1454125711647</v>
       </c>
       <c r="L44" t="n">
-        <v>417.6046363682045</v>
+        <v>417.6612145504505</v>
       </c>
       <c r="M44" t="n">
         <v>449.5135334928325</v>
@@ -11356,25 +11356,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K45" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L45" t="n">
-        <v>229.6093331288462</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M45" t="n">
-        <v>142.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N45" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O45" t="n">
-        <v>383.5962444444444</v>
+        <v>382.6009056104135</v>
       </c>
       <c r="P45" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q45" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R45" t="n">
         <v>45.52166981132082</v>
@@ -22558,22 +22558,22 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T2" t="n">
-        <v>223.0958495641314</v>
+        <v>10.81046392068936</v>
       </c>
       <c r="U2" t="n">
         <v>251.3456529078365</v>
       </c>
       <c r="V2" t="n">
-        <v>86.7522584701349</v>
+        <v>86.73796959247585</v>
       </c>
       <c r="W2" t="n">
-        <v>108.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X2" t="n">
-        <v>128.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y2" t="n">
-        <v>173.9651386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="3">
@@ -22583,13 +22583,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>27.31724297911936</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>121.2443095168948</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -22631,7 +22631,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>171.6831711038378</v>
@@ -22683,13 +22683,13 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I4" t="n">
-        <v>137.8921792844459</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -22704,13 +22704,13 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>177.2933913771695</v>
+        <v>132.9899077786023</v>
       </c>
       <c r="S4" t="n">
         <v>224.0165980369723</v>
@@ -22741,31 +22741,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>382.7338416634806</v>
+        <v>141.7195527858215</v>
       </c>
       <c r="C5" t="n">
         <v>365.2728917710076</v>
       </c>
       <c r="D5" t="n">
-        <v>354.683041620683</v>
+        <v>113.6687527430239</v>
       </c>
       <c r="E5" t="n">
-        <v>381.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F5" t="n">
-        <v>176.02842466673</v>
+        <v>194.5906600982693</v>
       </c>
       <c r="G5" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H5" t="n">
-        <v>98.47480211576715</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -22820,13 +22820,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>27.31724297911936</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -22838,13 +22838,13 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -22889,7 +22889,7 @@
         <v>205.7729852034775</v>
       </c>
       <c r="Y6" t="n">
-        <v>205.6826957773044</v>
+        <v>49.65393615106379</v>
       </c>
     </row>
     <row r="7">
@@ -22911,7 +22911,7 @@
         <v>146.4339626465692</v>
       </c>
       <c r="F7" t="n">
-        <v>127.8627523801189</v>
+        <v>145.4210480229312</v>
       </c>
       <c r="G7" t="n">
         <v>167.9909793584588</v>
@@ -22923,10 +22923,10 @@
         <v>155.4504749272583</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -22956,7 +22956,7 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U7" t="n">
-        <v>286.3190293564909</v>
+        <v>153.1320617711229</v>
       </c>
       <c r="V7" t="n">
         <v>252.137643323828</v>
@@ -22978,13 +22978,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>141.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C8" t="n">
-        <v>124.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D8" t="n">
-        <v>354.683041620683</v>
+        <v>113.6687527430239</v>
       </c>
       <c r="E8" t="n">
         <v>381.9303700722618</v>
@@ -22996,13 +22996,13 @@
         <v>415.302737515135</v>
       </c>
       <c r="H8" t="n">
-        <v>339.4748021157671</v>
+        <v>98.46051323810809</v>
       </c>
       <c r="I8" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -23023,13 +23023,13 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>209.0200695862453</v>
+        <v>138.0053911458572</v>
       </c>
       <c r="T8" t="n">
         <v>223.0958495641314</v>
@@ -23044,10 +23044,10 @@
         <v>349.240968717413</v>
       </c>
       <c r="X8" t="n">
-        <v>157.4583006784691</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y8" t="n">
-        <v>145.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="9">
@@ -23060,7 +23060,7 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C9" t="n">
-        <v>27.31724297911936</v>
+        <v>27.26179070270013</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -23157,13 +23157,13 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I10" t="n">
-        <v>155.4504749272583</v>
+        <v>137.8921792844459</v>
       </c>
       <c r="J10" t="n">
-        <v>93.35918011667277</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -23178,13 +23178,13 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R10" t="n">
-        <v>132.9899077786024</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S10" t="n">
         <v>224.0165980369723</v>
@@ -23221,22 +23221,22 @@
         <v>365.2728917710076</v>
       </c>
       <c r="D11" t="n">
-        <v>354.683041620683</v>
+        <v>352.8735455476468</v>
       </c>
       <c r="E11" t="n">
-        <v>381.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F11" t="n">
-        <v>406.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G11" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H11" t="n">
         <v>339.4748021157671</v>
       </c>
       <c r="I11" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>11.94928935461252</v>
@@ -23275,16 +23275,16 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V11" t="n">
-        <v>115.4794584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W11" t="n">
-        <v>108.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X11" t="n">
-        <v>128.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y11" t="n">
-        <v>145.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="12">
@@ -23297,7 +23297,7 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C12" t="n">
-        <v>58.48575304063304</v>
+        <v>96.72412754501165</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -23318,7 +23318,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -23342,10 +23342,10 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
         <v>200.1647286948216</v>
@@ -23354,7 +23354,7 @@
         <v>225.9413820809748</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W12" t="n">
         <v>251.6949831609196</v>
@@ -23421,7 +23421,7 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>132.9899077786024</v>
+        <v>132.9899077786023</v>
       </c>
       <c r="S13" t="n">
         <v>224.0165980369723</v>
@@ -23452,10 +23452,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>382.7338416634806</v>
+        <v>170.4484560200385</v>
       </c>
       <c r="C14" t="n">
-        <v>124.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D14" t="n">
         <v>354.683041620683</v>
@@ -23464,7 +23464,7 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F14" t="n">
-        <v>165.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G14" t="n">
         <v>415.302737515135</v>
@@ -23515,13 +23515,13 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W14" t="n">
-        <v>349.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X14" t="n">
-        <v>157.4583006784691</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y14" t="n">
-        <v>145.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="15">
@@ -23537,13 +23537,13 @@
         <v>172.7084989883157</v>
       </c>
       <c r="D15" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>21.52433192206654</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -23552,7 +23552,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>26.23646281822215</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -23579,13 +23579,13 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U15" t="n">
         <v>225.9413820809748</v>
@@ -23628,7 +23628,7 @@
         <v>167.9909793584588</v>
       </c>
       <c r="H16" t="n">
-        <v>29.04020492207155</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I16" t="n">
         <v>155.4504749272583</v>
@@ -23652,13 +23652,13 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>177.2933913771695</v>
+        <v>132.9899077786023</v>
       </c>
       <c r="S16" t="n">
         <v>224.0165980369723</v>
@@ -23701,16 +23701,16 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F17" t="n">
-        <v>383.0899041129076</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G17" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H17" t="n">
-        <v>98.47480211576715</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J17" t="n">
         <v>11.94928935461252</v>
@@ -23737,19 +23737,19 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>138.6760617849701</v>
       </c>
       <c r="T17" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>251.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V17" t="n">
-        <v>327.7522584701349</v>
+        <v>86.73796959247585</v>
       </c>
       <c r="W17" t="n">
         <v>349.240968717413</v>
@@ -23768,31 +23768,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>21.52433192206654</v>
+        <v>125.9137940316683</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -23822,7 +23822,7 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U18" t="n">
         <v>225.9413820809748</v>
@@ -23898,13 +23898,13 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S19" t="n">
-        <v>90.82963045160423</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T19" t="n">
         <v>227.9455894282815</v>
       </c>
       <c r="U19" t="n">
-        <v>286.3190293564909</v>
+        <v>153.1320617711229</v>
       </c>
       <c r="V19" t="n">
         <v>252.137643323828</v>
@@ -23938,10 +23938,10 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F20" t="n">
-        <v>406.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G20" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H20" t="n">
         <v>339.4748021157671</v>
@@ -23971,25 +23971,25 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>149.8691179411497</v>
       </c>
       <c r="S20" t="n">
-        <v>209.0200695862453</v>
+        <v>6.725383157348119</v>
       </c>
       <c r="T20" t="n">
-        <v>10.8230495641314</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U20" t="n">
-        <v>10.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V20" t="n">
-        <v>86.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W20" t="n">
-        <v>108.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X20" t="n">
         <v>369.731100678469</v>
@@ -24008,25 +24008,25 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C21" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>147.4450655646388</v>
       </c>
       <c r="E21" t="n">
-        <v>83.78295398104913</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J21" t="n">
         <v>0.7465913262578567</v>
@@ -24056,25 +24056,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T21" t="n">
         <v>200.1647286948216</v>
       </c>
       <c r="U21" t="n">
-        <v>225.9413820809748</v>
+        <v>142.9094900234331</v>
       </c>
       <c r="V21" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X21" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="22">
@@ -24135,7 +24135,7 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S22" t="n">
-        <v>224.0165980369723</v>
+        <v>90.82963045160423</v>
       </c>
       <c r="T22" t="n">
         <v>227.9455894282815</v>
@@ -24150,7 +24150,7 @@
         <v>286.522998336591</v>
       </c>
       <c r="X22" t="n">
-        <v>92.52268780366913</v>
+        <v>225.7096553890372</v>
       </c>
       <c r="Y22" t="n">
         <v>218.5846533520948</v>
@@ -24163,22 +24163,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>141.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C23" t="n">
-        <v>124.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D23" t="n">
-        <v>142.4102416206829</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E23" t="n">
-        <v>381.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F23" t="n">
         <v>406.8760457417114</v>
       </c>
       <c r="G23" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H23" t="n">
         <v>339.4748021157671</v>
@@ -24208,7 +24208,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>149.8691179411497</v>
@@ -24220,13 +24220,13 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U23" t="n">
-        <v>251.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V23" t="n">
-        <v>327.7522584701349</v>
+        <v>125.4575720412377</v>
       </c>
       <c r="W23" t="n">
-        <v>349.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X23" t="n">
         <v>369.731100678469</v>
@@ -24242,19 +24242,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D24" t="n">
         <v>147.4450655646388</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -24263,10 +24263,10 @@
         <v>112.2354442364965</v>
       </c>
       <c r="I24" t="n">
-        <v>89.39663285141508</v>
+        <v>36.22226829029555</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -24290,13 +24290,13 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>149.4992429516138</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
         <v>225.9413820809748</v>
@@ -24311,7 +24311,7 @@
         <v>205.7729852034775</v>
       </c>
       <c r="Y24" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -24412,19 +24412,19 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F26" t="n">
-        <v>176.02842466673</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G26" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H26" t="n">
-        <v>98.47480211576715</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -24445,22 +24445,22 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>251.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V26" t="n">
-        <v>327.7522584701349</v>
+        <v>225.414031377446</v>
       </c>
       <c r="W26" t="n">
         <v>349.240968717413</v>
@@ -24479,7 +24479,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C27" t="n">
         <v>172.7084989883157</v>
@@ -24488,7 +24488,7 @@
         <v>147.4450655646388</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F27" t="n">
         <v>145.0692123933839</v>
@@ -24503,7 +24503,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -24527,28 +24527,28 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>33.16173223547548</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>251.6949831609196</v>
+        <v>247.8610253924609</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="28">
@@ -24603,10 +24603,10 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q28" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>177.2933913771695</v>
+        <v>130.2684670434958</v>
       </c>
       <c r="S28" t="n">
         <v>224.0165980369723</v>
@@ -24621,7 +24621,7 @@
         <v>252.137643323828</v>
       </c>
       <c r="W28" t="n">
-        <v>153.336030751223</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X28" t="n">
         <v>225.7096553890372</v>
@@ -24661,7 +24661,7 @@
         <v>210.4758895704059</v>
       </c>
       <c r="J29" t="n">
-        <v>11.94928935452493</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -24685,28 +24685,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R29" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>209.0200695862453</v>
+        <v>128.6853625704253</v>
       </c>
       <c r="T29" t="n">
-        <v>10.82304956406634</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>10.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V29" t="n">
-        <v>327.7522584701349</v>
+        <v>86.73796959247585</v>
       </c>
       <c r="W29" t="n">
         <v>349.240968717413</v>
       </c>
       <c r="X29" t="n">
-        <v>128.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y29" t="n">
-        <v>145.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="30">
@@ -24716,16 +24716,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>157.6450804554009</v>
+        <v>115.6878816063606</v>
       </c>
       <c r="F30" t="n">
         <v>145.0692123933839</v>
@@ -24734,13 +24734,13 @@
         <v>137.3435171632106</v>
       </c>
       <c r="H30" t="n">
-        <v>62.21891236670356</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I30" t="n">
         <v>89.39663285141508</v>
       </c>
       <c r="J30" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -24770,22 +24770,22 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T30" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
         <v>225.9413820809748</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W30" t="n">
-        <v>10.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="31">
@@ -24801,10 +24801,10 @@
         <v>167.2468210986278</v>
       </c>
       <c r="D31" t="n">
-        <v>15.42850543284433</v>
+        <v>148.6154730182124</v>
       </c>
       <c r="E31" t="n">
-        <v>146.4339626465692</v>
+        <v>13.24699506120118</v>
       </c>
       <c r="F31" t="n">
         <v>145.4210480229312</v>
@@ -24880,16 +24880,16 @@
         <v>365.2728917710076</v>
       </c>
       <c r="D32" t="n">
-        <v>354.683041620683</v>
+        <v>113.6687527430239</v>
       </c>
       <c r="E32" t="n">
-        <v>381.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F32" t="n">
-        <v>165.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G32" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H32" t="n">
         <v>339.4748021157671</v>
@@ -24931,19 +24931,19 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U32" t="n">
-        <v>251.3456529078365</v>
+        <v>39.0602672643945</v>
       </c>
       <c r="V32" t="n">
         <v>327.7522584701349</v>
       </c>
       <c r="W32" t="n">
-        <v>349.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X32" t="n">
-        <v>157.4583006784691</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y32" t="n">
-        <v>145.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="33">
@@ -24956,28 +24956,28 @@
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>112.2354442364965</v>
+        <v>48.72576195918361</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -25013,16 +25013,16 @@
         <v>225.9413820809748</v>
       </c>
       <c r="V33" t="n">
-        <v>205.9132846314895</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W33" t="n">
-        <v>10.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="34">
@@ -25095,10 +25095,10 @@
         <v>252.137643323828</v>
       </c>
       <c r="W34" t="n">
-        <v>286.522998336591</v>
+        <v>153.336030751223</v>
       </c>
       <c r="X34" t="n">
-        <v>92.52268780366913</v>
+        <v>225.7096553890372</v>
       </c>
       <c r="Y34" t="n">
         <v>218.5846533520948</v>
@@ -25117,19 +25117,19 @@
         <v>365.2728917710076</v>
       </c>
       <c r="D35" t="n">
-        <v>113.683041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E35" t="n">
         <v>381.9303700722618</v>
       </c>
       <c r="F35" t="n">
-        <v>165.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G35" t="n">
         <v>415.302737515135</v>
       </c>
       <c r="H35" t="n">
-        <v>98.47480211576715</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I35" t="n">
         <v>210.4758895704059</v>
@@ -25159,22 +25159,22 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R35" t="n">
-        <v>149.8691179410846</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>209.0200695862453</v>
       </c>
       <c r="T35" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>251.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V35" t="n">
-        <v>115.4794584701349</v>
+        <v>247.4175514543149</v>
       </c>
       <c r="W35" t="n">
-        <v>349.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X35" t="n">
         <v>369.731100678469</v>
@@ -25190,7 +25190,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -25199,7 +25199,7 @@
         <v>147.4450655646388</v>
       </c>
       <c r="E36" t="n">
-        <v>0.09724602031360519</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F36" t="n">
         <v>145.0692123933839</v>
@@ -25208,13 +25208,13 @@
         <v>137.3435171632106</v>
       </c>
       <c r="H36" t="n">
-        <v>112.2354442364965</v>
+        <v>104.1835801337703</v>
       </c>
       <c r="I36" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -25247,7 +25247,7 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U36" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -25311,13 +25311,13 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R37" t="n">
-        <v>177.2933913771695</v>
+        <v>44.10642379180146</v>
       </c>
       <c r="S37" t="n">
         <v>224.0165980369723</v>
@@ -25329,7 +25329,7 @@
         <v>286.3190293564909</v>
       </c>
       <c r="V37" t="n">
-        <v>207.8341597252609</v>
+        <v>252.137643323828</v>
       </c>
       <c r="W37" t="n">
         <v>286.522998336591</v>
@@ -25348,13 +25348,13 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>141.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C38" t="n">
-        <v>124.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D38" t="n">
-        <v>354.683041620683</v>
+        <v>113.6687527430239</v>
       </c>
       <c r="E38" t="n">
         <v>381.9303700722618</v>
@@ -25393,7 +25393,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R38" t="n">
         <v>149.8691179411497</v>
@@ -25405,19 +25405,19 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U38" t="n">
-        <v>251.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V38" t="n">
         <v>327.7522584701349</v>
       </c>
       <c r="W38" t="n">
-        <v>349.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X38" t="n">
-        <v>167.4489998930138</v>
+        <v>157.4457150350269</v>
       </c>
       <c r="Y38" t="n">
-        <v>145.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="39">
@@ -25436,19 +25436,19 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>94.86215266454575</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J39" t="n">
         <v>0.7465913262578567</v>
@@ -25490,13 +25490,13 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W39" t="n">
-        <v>10.69498316091961</v>
+        <v>12.61099459313158</v>
       </c>
       <c r="X39" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -25560,7 +25560,7 @@
         <v>224.0165980369723</v>
       </c>
       <c r="T40" t="n">
-        <v>227.9455894282815</v>
+        <v>94.7586218429135</v>
       </c>
       <c r="U40" t="n">
         <v>286.3190293564909</v>
@@ -25569,7 +25569,7 @@
         <v>252.137643323828</v>
       </c>
       <c r="W40" t="n">
-        <v>153.336030751223</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X40" t="n">
         <v>225.7096553890372</v>
@@ -25585,16 +25585,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>382.7338416634806</v>
+        <v>141.7195527858215</v>
       </c>
       <c r="C41" t="n">
-        <v>124.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D41" t="n">
-        <v>113.683041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E41" t="n">
-        <v>191.5975586414191</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F41" t="n">
         <v>406.8760457417114</v>
@@ -25603,13 +25603,13 @@
         <v>415.302737515135</v>
       </c>
       <c r="H41" t="n">
-        <v>339.4748021157671</v>
+        <v>98.46051323810809</v>
       </c>
       <c r="I41" t="n">
         <v>210.4758895704059</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -25630,7 +25630,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R41" t="n">
         <v>149.8691179411497</v>
@@ -25642,13 +25642,13 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U41" t="n">
-        <v>251.3456529078365</v>
+        <v>39.0602672643945</v>
       </c>
       <c r="V41" t="n">
         <v>327.7522584701349</v>
       </c>
       <c r="W41" t="n">
-        <v>108.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X41" t="n">
         <v>369.731100678469</v>
@@ -25664,16 +25664,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>95.60874399080365</v>
+        <v>104.3983415011525</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -25685,7 +25685,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -25727,7 +25727,7 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W42" t="n">
-        <v>10.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X42" t="n">
         <v>205.7729852034775</v>
@@ -25791,7 +25791,7 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R43" t="n">
-        <v>177.2933913771695</v>
+        <v>44.10642379180146</v>
       </c>
       <c r="S43" t="n">
         <v>224.0165980369723</v>
@@ -25806,7 +25806,7 @@
         <v>252.137643323828</v>
       </c>
       <c r="W43" t="n">
-        <v>153.336030751223</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X43" t="n">
         <v>225.7096553890372</v>
@@ -25825,25 +25825,25 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C44" t="n">
-        <v>365.2728917710076</v>
+        <v>152.9875061275656</v>
       </c>
       <c r="D44" t="n">
         <v>354.683041620683</v>
       </c>
       <c r="E44" t="n">
-        <v>381.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F44" t="n">
-        <v>165.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G44" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H44" t="n">
         <v>339.4748021157671</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J44" t="n">
         <v>11.94928935461252</v>
@@ -25867,19 +25867,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R44" t="n">
         <v>149.8691179411497</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U44" t="n">
-        <v>209.655360843164</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V44" t="n">
         <v>327.7522584701349</v>
@@ -25904,28 +25904,28 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C45" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E45" t="n">
-        <v>6.212111139388554</v>
+        <v>6.645736842900988</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I45" t="n">
         <v>89.39663285141508</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -25955,7 +25955,7 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T45" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
         <v>225.9413820809748</v>
@@ -25964,13 +25964,13 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W45" t="n">
-        <v>10.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X45" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -26037,7 +26037,7 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U46" t="n">
-        <v>153.1320617711229</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V46" t="n">
         <v>252.137643323828</v>
@@ -26049,7 +26049,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y46" t="n">
-        <v>218.5846533520948</v>
+        <v>85.39768576672677</v>
       </c>
     </row>
   </sheetData>
@@ -26078,7 +26078,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>481856.1408331657</v>
+        <v>481865.9503408644</v>
       </c>
     </row>
     <row r="3">
@@ -26086,7 +26086,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>481856.1408331657</v>
+        <v>481865.9503408644</v>
       </c>
     </row>
     <row r="4">
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>481856.1408331658</v>
+        <v>481865.9503408642</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>481856.1408331657</v>
+        <v>481865.9503408644</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>481856.1408331657</v>
+        <v>481865.9503408644</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>481856.1408331657</v>
+        <v>481865.9503408641</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>481856.1408331657</v>
+        <v>481865.9503408641</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>481856.1408331658</v>
+        <v>481865.9503408644</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>481856.1408331657</v>
+        <v>481865.9503408642</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>481856.1408331832</v>
+        <v>481865.9503408641</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>481856.1408331657</v>
+        <v>481865.9503408644</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>481856.1408331731</v>
+        <v>481865.9503408642</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>481856.1408331657</v>
+        <v>481865.9503408642</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>481856.1408331657</v>
+        <v>481865.9503408642</v>
       </c>
     </row>
     <row r="16">
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>481856.1408331656</v>
+        <v>481865.9503408644</v>
       </c>
     </row>
   </sheetData>
@@ -26261,49 +26261,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>99694.37396548245</v>
+        <v>99696.40351879936</v>
       </c>
       <c r="C2" t="n">
-        <v>99694.37396548242</v>
+        <v>99696.40351879939</v>
       </c>
       <c r="D2" t="n">
-        <v>99694.37396548245</v>
+        <v>99696.40351879939</v>
       </c>
       <c r="E2" t="n">
-        <v>99694.37396548249</v>
+        <v>99696.40351879936</v>
       </c>
       <c r="F2" t="n">
-        <v>99694.37396548249</v>
+        <v>99696.40351879939</v>
       </c>
       <c r="G2" t="n">
-        <v>99694.37396548245</v>
+        <v>99696.40351879937</v>
       </c>
       <c r="H2" t="n">
-        <v>99694.37396548243</v>
+        <v>99696.40351879939</v>
       </c>
       <c r="I2" t="n">
-        <v>99694.37396548246</v>
+        <v>99696.40351879936</v>
       </c>
       <c r="J2" t="n">
-        <v>99694.37396548242</v>
+        <v>99696.40351879937</v>
       </c>
       <c r="K2" t="n">
-        <v>99694.37396548608</v>
+        <v>99696.40351879939</v>
       </c>
       <c r="L2" t="n">
-        <v>99694.37396548246</v>
+        <v>99696.40351879942</v>
       </c>
       <c r="M2" t="n">
-        <v>99694.373965484</v>
+        <v>99696.40351879937</v>
       </c>
       <c r="N2" t="n">
-        <v>99694.37396548245</v>
+        <v>99696.40351879939</v>
       </c>
       <c r="O2" t="n">
-        <v>99694.37396548243</v>
+        <v>99696.4035187994</v>
       </c>
       <c r="P2" t="n">
-        <v>99694.37396548243</v>
+        <v>99696.40351879942</v>
       </c>
     </row>
     <row r="3">
@@ -26313,7 +26313,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80764.643</v>
+        <v>80769.43153154773</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -26337,7 +26337,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>63056.204</v>
+        <v>63059.94259910623</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>179.5221438966159</v>
+        <v>3448.117877250231</v>
       </c>
       <c r="C4" t="n">
-        <v>179.5221438966159</v>
+        <v>3448.117877250231</v>
       </c>
       <c r="D4" t="n">
-        <v>179.5221438966159</v>
+        <v>3448.117877250231</v>
       </c>
       <c r="E4" t="n">
-        <v>179.5221438966159</v>
+        <v>3448.11787725023</v>
       </c>
       <c r="F4" t="n">
-        <v>179.5221438966159</v>
+        <v>3448.11787725023</v>
       </c>
       <c r="G4" t="n">
-        <v>179.5221438966159</v>
+        <v>3448.117877250231</v>
       </c>
       <c r="H4" t="n">
-        <v>179.5221438966159</v>
+        <v>3448.117877250231</v>
       </c>
       <c r="I4" t="n">
-        <v>179.5221438966159</v>
+        <v>3448.11787725023</v>
       </c>
       <c r="J4" t="n">
-        <v>179.5221438966159</v>
+        <v>3448.117877250231</v>
       </c>
       <c r="K4" t="n">
-        <v>179.5221438966345</v>
+        <v>3448.117877250231</v>
       </c>
       <c r="L4" t="n">
-        <v>179.5221438966159</v>
+        <v>3448.117877250231</v>
       </c>
       <c r="M4" t="n">
-        <v>179.5221438966238</v>
+        <v>3448.117877250231</v>
       </c>
       <c r="N4" t="n">
-        <v>179.5221438966159</v>
+        <v>3448.117877250231</v>
       </c>
       <c r="O4" t="n">
-        <v>179.5221438966159</v>
+        <v>3448.117877250231</v>
       </c>
       <c r="P4" t="n">
-        <v>179.5221438966159</v>
+        <v>3448.117877250231</v>
       </c>
     </row>
     <row r="5">
@@ -26417,49 +26417,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>48280.39999999999</v>
+        <v>48281.26876376167</v>
       </c>
       <c r="C5" t="n">
-        <v>48280.39999999999</v>
+        <v>48281.26876376167</v>
       </c>
       <c r="D5" t="n">
-        <v>48280.39999999999</v>
+        <v>48281.26876376167</v>
       </c>
       <c r="E5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="F5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="G5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="H5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="I5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="J5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="K5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="L5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="M5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="N5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="O5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="P5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
     </row>
     <row r="6">
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-29530.19117841416</v>
+        <v>-32802.41465376027</v>
       </c>
       <c r="C6" t="n">
-        <v>51234.45182158581</v>
+        <v>47967.01687778749</v>
       </c>
       <c r="D6" t="n">
-        <v>51234.45182158584</v>
+        <v>47967.01687778749</v>
       </c>
       <c r="E6" t="n">
-        <v>84862.05182158588</v>
+        <v>81594.61687778746</v>
       </c>
       <c r="F6" t="n">
-        <v>84862.05182158588</v>
+        <v>81594.61687778748</v>
       </c>
       <c r="G6" t="n">
-        <v>84862.05182158583</v>
+        <v>81594.61687778747</v>
       </c>
       <c r="H6" t="n">
-        <v>84862.05182158582</v>
+        <v>81594.61687778748</v>
       </c>
       <c r="I6" t="n">
-        <v>84862.05182158585</v>
+        <v>81594.61687778746</v>
       </c>
       <c r="J6" t="n">
-        <v>21805.8478215858</v>
+        <v>18534.67427868124</v>
       </c>
       <c r="K6" t="n">
-        <v>84862.05182158944</v>
+        <v>81594.61687778748</v>
       </c>
       <c r="L6" t="n">
-        <v>84862.05182158585</v>
+        <v>81594.61687778751</v>
       </c>
       <c r="M6" t="n">
-        <v>84862.05182158737</v>
+        <v>81594.61687778747</v>
       </c>
       <c r="N6" t="n">
-        <v>84862.05182158583</v>
+        <v>81594.61687778748</v>
       </c>
       <c r="O6" t="n">
-        <v>84862.05182158582</v>
+        <v>81594.6168777875</v>
       </c>
       <c r="P6" t="n">
-        <v>84862.05182158582</v>
+        <v>81594.61687778751</v>
       </c>
     </row>
   </sheetData>
@@ -26727,49 +26727,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="L4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="M4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
   </sheetData>
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26895,16 +26895,16 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -26913,28 +26913,28 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26944,49 +26944,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27185,7 +27185,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -34626,7 +34626,7 @@
         <v>207.9338608153932</v>
       </c>
       <c r="O2" t="n">
-        <v>150.6453916588127</v>
+        <v>150.7019698410586</v>
       </c>
       <c r="P2" t="n">
         <v>90.5657124162131</v>
@@ -34693,22 +34693,22 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L3" t="n">
-        <v>161.1671126127986</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M3" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N3" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>241</v>
+        <v>99.8112771299739</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q3" t="n">
         <v>70.09551364982758</v>
@@ -34860,7 +34860,7 @@
         <v>219.1673002655598</v>
       </c>
       <c r="N5" t="n">
-        <v>207.8772826331474</v>
+        <v>207.9338608153932</v>
       </c>
       <c r="O5" t="n">
         <v>150.7019698410586</v>
@@ -34930,25 +34930,25 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>91.05495334897203</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N6" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O6" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P6" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q6" t="n">
-        <v>70.09551364982758</v>
+        <v>46.78797658628819</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -35103,7 +35103,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P8" t="n">
-        <v>90.50913423396717</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -35167,25 +35167,25 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M9" t="n">
-        <v>43.25734905099399</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N9" t="n">
-        <v>241</v>
+        <v>240.0046611659691</v>
       </c>
       <c r="O9" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -35325,7 +35325,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L11" t="n">
         <v>181.8947995804632</v>
@@ -35404,25 +35404,25 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M12" t="n">
-        <v>217.6787513871916</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O12" t="n">
-        <v>241</v>
+        <v>169.9067907798016</v>
       </c>
       <c r="P12" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q12" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -35568,7 +35568,7 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M14" t="n">
-        <v>219.1107220833138</v>
+        <v>219.1673002655598</v>
       </c>
       <c r="N14" t="n">
         <v>207.9338608153932</v>
@@ -35641,25 +35641,25 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N15" t="n">
-        <v>169.8645014752148</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P15" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>55.51629994036219</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35814,7 +35814,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P17" t="n">
-        <v>90.50913423396717</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -35881,22 +35881,22 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>232.285965523585</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>55.48829951343433</v>
+        <v>217.7067518141195</v>
       </c>
       <c r="N18" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O18" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P18" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -36036,7 +36036,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L20" t="n">
         <v>181.8947995804632</v>
@@ -36115,25 +36115,25 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L21" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O21" t="n">
-        <v>169.8811470892137</v>
+        <v>113.3808631277494</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36273,7 +36273,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L23" t="n">
         <v>181.8947995804632</v>
@@ -36355,22 +36355,22 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M24" t="n">
-        <v>217.6787513871916</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N24" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O24" t="n">
-        <v>241</v>
+        <v>55.51629994036219</v>
       </c>
       <c r="P24" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q24" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36510,7 +36510,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L26" t="n">
         <v>181.8947995804632</v>
@@ -36589,19 +36589,19 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L27" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M27" t="n">
-        <v>241</v>
+        <v>99.81127712997396</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>226.3927858636067</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P27" t="n">
         <v>184.4883612256069</v>
@@ -36762,7 +36762,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P29" t="n">
-        <v>90.5091342341229</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -36832,19 +36832,19 @@
         <v>232.285965523585</v>
       </c>
       <c r="M30" t="n">
-        <v>169.8811470892136</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N30" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O30" t="n">
-        <v>241</v>
+        <v>240.0046611659691</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -36999,7 +36999,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P32" t="n">
-        <v>90.50913423396717</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -37066,22 +37066,22 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M33" t="n">
-        <v>241</v>
+        <v>240.0046611659691</v>
       </c>
       <c r="N33" t="n">
-        <v>217.6787513871916</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O33" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P33" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37236,7 +37236,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P35" t="n">
-        <v>90.50913423403355</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -37300,25 +37300,25 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M36" t="n">
-        <v>99.76898782538704</v>
+        <v>240.0046611659691</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O36" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P36" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37458,7 +37458,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L38" t="n">
         <v>181.8947995804632</v>
@@ -37537,25 +37537,25 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M39" t="n">
-        <v>113.3528627008216</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N39" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O39" t="n">
-        <v>241</v>
+        <v>169.9091475161414</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -37695,13 +37695,13 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L41" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M41" t="n">
-        <v>219.1673002655598</v>
+        <v>219.1673002655597</v>
       </c>
       <c r="N41" t="n">
         <v>207.9338608153932</v>
@@ -37777,22 +37777,22 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>232.285965523585</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N42" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O42" t="n">
-        <v>55.48829951343442</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P42" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>46.78797658628819</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -37935,7 +37935,7 @@
         <v>104.0555615261842</v>
       </c>
       <c r="L44" t="n">
-        <v>181.8382213982173</v>
+        <v>181.8947995804632</v>
       </c>
       <c r="M44" t="n">
         <v>219.1673002655598</v>
@@ -38011,25 +38011,25 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>91.05495334897203</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N45" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O45" t="n">
-        <v>241</v>
+        <v>240.0046611659691</v>
       </c>
       <c r="P45" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
